--- a/XLibur.Tests/Resource/Examples/Misc/DataTypes.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/DataTypes.xlsx
@@ -469,27 +469,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C22"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="21.424911" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.140625"/>
+    <x:col min="2" max="2" width="22.710625" customWidth="1"/>
+    <x:col min="3" max="3" width="21.424911" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:3">
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C3" s="1">
@@ -497,7 +494,7 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
-      <x:c r="B4" s="0" t="s">
+      <x:c r="B4" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="2">
@@ -505,23 +502,23 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
-      <x:c r="B5" s="0" t="s">
+      <x:c r="B5" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="b">
+      <x:c r="C5" t="b">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
-      <x:c r="B6" s="0" t="s">
+      <x:c r="B6" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C6" s="0">
+      <x:c r="C6">
         <x:v>123.45</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
-      <x:c r="B7" s="0" t="s">
+      <x:c r="B7" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="3">
@@ -529,15 +526,15 @@
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
-      <x:c r="B9" s="0" t="s">
+      <x:c r="B9" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C9" s="0">
+      <x:c r="C9">
         <x:v>9.999E+307</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
-      <x:c r="B11" s="0" t="s">
+      <x:c r="B11" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
@@ -545,7 +542,7 @@
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
-      <x:c r="B12" s="0" t="s">
+      <x:c r="B12" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
@@ -553,7 +550,7 @@
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
-      <x:c r="B13" s="0" t="s">
+      <x:c r="B13" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
@@ -561,7 +558,7 @@
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
-      <x:c r="B14" s="0" t="s">
+      <x:c r="B14" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
@@ -569,7 +566,7 @@
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
-      <x:c r="B15" s="0" t="s">
+      <x:c r="B15" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="C15" s="4" t="s">
@@ -577,7 +574,7 @@
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
-      <x:c r="B16" s="0" t="s">
+      <x:c r="B16" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="5">
@@ -585,7 +582,7 @@
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
-      <x:c r="B17" s="0" t="s">
+      <x:c r="B17" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="C17" s="5">
@@ -593,7 +590,7 @@
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
-      <x:c r="B18" s="0" t="s">
+      <x:c r="B18" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C18" s="4" t="s">
@@ -601,37 +598,33 @@
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
-      <x:c r="B19" s="0" t="s">
+      <x:c r="B19" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C19" s="0" t="inlineStr">
+      <x:c r="C19" t="inlineStr">
         <x:is>
           <x:t>Not Shared</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
-      <x:c r="B21" s="0" t="s">
+      <x:c r="B21" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C21" s="0" t="e">
+      <x:c r="C21" t="e">
         <x:v>#VALUE!</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
-      <x:c r="B22" s="0" t="s">
+      <x:c r="B22" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C22" s="0" t="e">
+      <x:c r="C22" t="e">
         <x:f>1/0</x:f>
         <x:v>#DIV/0!</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Misc/DataTypes.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/DataTypes.xlsx
@@ -498,7 +498,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="2">
-        <x:v>40423.5731712963</x:v>
+        <x:v>40423.573171296295</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
@@ -522,7 +522,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="3">
-        <x:v>1.40650462962963</x:v>
+        <x:v>1.4065046296296295</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">

--- a/XLibur.Tests/Resource/Examples/Misc/DataTypes.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/DataTypes.xlsx
@@ -473,8 +473,8 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="22.710625" customWidth="1"/>
-    <x:col min="3" max="3" width="21.424911" customWidth="1"/>
+    <x:col min="2" max="2" width="21.996339" customWidth="1"/>
+    <x:col min="3" max="3" width="20.853482" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:3">

--- a/XLibur.Tests/Resource/Examples/Misc/DataTypes.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/DataTypes.xlsx
@@ -472,9 +472,9 @@
   <x:dimension ref="A1:C22"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="21.996339" customWidth="1"/>
-    <x:col min="3" max="3" width="20.853482" customWidth="1"/>
+    <x:col min="1" max="1" width="9.144286"/>
+    <x:col min="2" max="2" width="22" customWidth="1"/>
+    <x:col min="3" max="3" width="20.857143" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:3">
